--- a/BWI/bestwine_output/bestwine_Guadeloupe.xlsx
+++ b/BWI/bestwine_output/bestwine_Guadeloupe.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1759,6 +1759,99 @@
       <c r="Z12" s="3" t="inlineStr"/>
       <c r="AA12" s="3" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Primantilles</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Primantilles</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>90647</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Guadeloupe</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Baie Mahault</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Basse-Terre, Canton de Baie-Mahault-1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Moudong Sud</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>97122</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://primantilles.com</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>contact@primantilles.fr</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>+590 590 26 51 96</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>92205155200011</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gourmetshop971/</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gourmetshop971</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Guadeloupe.xlsx
+++ b/BWI/bestwine_output/bestwine_Guadeloupe.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1852,6 +1852,99 @@
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Primantilles</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Primantilles</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>90647</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Guadeloupe</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Baie Mahault</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Basse-Terre, Canton de Baie-Mahault-1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Moudong Sud</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97122</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://primantilles.com</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>contact@primantilles.fr</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>+590 590 26 51 96</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>92205155200011</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gourmetshop971/</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gourmetshop971</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
